--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios168.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios168.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19286.79721988016</v>
+        <v>27413.76392517078</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22752.27957501764</v>
+        <v>19139.8172828729</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18409.53428563238</v>
+        <v>15092.58642905197</v>
       </c>
     </row>
     <row r="9">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19713.20449769126</v>
+        <v>16457.82984916801</v>
       </c>
     </row>
     <row r="12">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4928.301124422816</v>
+        <v>4114.457462292004</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39098.38793249235</v>
+        <v>61243.32556167692</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9208.934911764105</v>
+        <v>11472.0819673223</v>
       </c>
     </row>
     <row r="18">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>27495.39497188891</v>
+        <v>12092.14655777753</v>
       </c>
     </row>
     <row r="21">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>15001.38993642093</v>
+        <v>17631.87819639297</v>
       </c>
     </row>
     <row r="24">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11572.49013538843</v>
+        <v>10885.94484242268</v>
       </c>
     </row>
     <row r="27">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>21999.38320994013</v>
+        <v>28209.13414249147</v>
       </c>
     </row>
     <row r="30">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5499.845802485033</v>
+        <v>7052.283535622867</v>
       </c>
     </row>
     <row r="32">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>69487.24730821501</v>
+        <v>63517.15445793838</v>
       </c>
     </row>
     <row r="33">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>15003.30530138749</v>
+        <v>18589.48029620803</v>
       </c>
     </row>
     <row r="36">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>19644.51161513366</v>
+        <v>37402.26412022394</v>
       </c>
     </row>
     <row r="39">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>33838.1448817279</v>
+        <v>20989.36896556814</v>
       </c>
     </row>
     <row r="42">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>11376.81860919696</v>
+        <v>11793.17427590439</v>
       </c>
     </row>
     <row r="45">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>12585.78186770355</v>
+        <v>17532.32045401677</v>
       </c>
     </row>
     <row r="48">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3146.445466925887</v>
+        <v>4383.080113504193</v>
       </c>
     </row>
     <row r="50">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>47419.37961101792</v>
+        <v>39927.34092048385</v>
       </c>
     </row>
     <row r="51">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>17893.13450429638</v>
+        <v>5594.394839988281</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>26239.30037548694</v>
+        <v>24889.39211487368</v>
       </c>
     </row>
     <row r="57">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>25093.9139824734</v>
+        <v>15358.25804716667</v>
       </c>
     </row>
     <row r="60">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>18639.5436676357</v>
+        <v>12371.85544424627</v>
       </c>
     </row>
     <row r="63">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11411.87091767344</v>
+        <v>32694.62485737791</v>
       </c>
     </row>
     <row r="66">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2852.96772941836</v>
+        <v>8173.656214344477</v>
       </c>
     </row>
     <row r="68">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>30716.01328920841</v>
+        <v>42359.82355503937</v>
       </c>
     </row>
     <row r="69">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440.575733874379</v>
+        <v>13230.40252110525</v>
       </c>
     </row>
     <row r="72">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>27794.86139860041</v>
+        <v>31799.86289356963</v>
       </c>
     </row>
     <row r="75">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26248.69845336343</v>
+        <v>27102.1846897443</v>
       </c>
     </row>
     <row r="78">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>18285.26137729916</v>
+        <v>13596.81570478361</v>
       </c>
     </row>
     <row r="81">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>21460.85046282062</v>
+        <v>17825.58539787152</v>
       </c>
     </row>
     <row r="84">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5365.212615705155</v>
+        <v>4456.39634946788</v>
       </c>
     </row>
     <row r="86">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>43937.64260781046</v>
+        <v>46521.83037408151</v>
       </c>
     </row>
     <row r="87">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>12506.7307732929</v>
+        <v>8899.960541795645</v>
       </c>
     </row>
     <row r="90">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>25882.80563845719</v>
+        <v>31345.33756667055</v>
       </c>
     </row>
     <row r="93">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>12461.79045003875</v>
+        <v>11938.81257539428</v>
       </c>
     </row>
     <row r="96">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>22663.74366625585</v>
+        <v>16141.58126893326</v>
       </c>
     </row>
     <row r="99">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>23119.22610861147</v>
+        <v>11577.80969152855</v>
       </c>
     </row>
     <row r="102">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5779.806527152869</v>
+        <v>2894.452422882137</v>
       </c>
     </row>
     <row r="104">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53150.12462033884</v>
+        <v>64439.10911114978</v>
       </c>
     </row>
     <row r="105">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>14806.86494104468</v>
+        <v>11173.18427670432</v>
       </c>
     </row>
     <row r="108">

--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios168.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios168.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27413.76392517078</v>
+        <v>39315.82205033302</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19139.8172828729</v>
+        <v>30203.69059642014</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15092.58642905197</v>
+        <v>14858.05185624786</v>
       </c>
     </row>
     <row r="9">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16457.82984916801</v>
+        <v>19702.97212360959</v>
       </c>
     </row>
     <row r="12">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4114.457462292004</v>
+        <v>4925.743030902398</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>61243.32556167692</v>
+        <v>63121.32015064409</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11472.0819673223</v>
+        <v>11290.22085199383</v>
       </c>
     </row>
     <row r="18">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>12092.14655777753</v>
+        <v>27117.83313399636</v>
       </c>
     </row>
     <row r="21">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17631.87819639297</v>
+        <v>18127.8021474658</v>
       </c>
     </row>
     <row r="24">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10885.94484242268</v>
+        <v>16397.90522086472</v>
       </c>
     </row>
     <row r="27">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>28209.13414249147</v>
+        <v>21743.62818357075</v>
       </c>
     </row>
     <row r="30">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7052.283535622867</v>
+        <v>5435.907045892687</v>
       </c>
     </row>
     <row r="32">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>63517.15445793838</v>
+        <v>79737.69595546815</v>
       </c>
     </row>
     <row r="33">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>18589.48029620803</v>
+        <v>21471.11893876159</v>
       </c>
     </row>
     <row r="36">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>37402.26412022394</v>
+        <v>30724.8958857486</v>
       </c>
     </row>
     <row r="39">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>20989.36896556814</v>
+        <v>25513.18983405927</v>
       </c>
     </row>
     <row r="42">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>11793.17427590439</v>
+        <v>8952.258079529118</v>
       </c>
     </row>
     <row r="45">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17532.32045401677</v>
+        <v>25428.49881955294</v>
       </c>
     </row>
     <row r="48">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4383.080113504193</v>
+        <v>6357.124704888236</v>
       </c>
     </row>
     <row r="50">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>39927.34092048385</v>
+        <v>53154.26845842842</v>
       </c>
     </row>
     <row r="51">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5594.394839988281</v>
+        <v>14517.63064682923</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>24889.39211487368</v>
+        <v>37973.40540592183</v>
       </c>
     </row>
     <row r="57">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>15358.25804716667</v>
+        <v>18816.8253350249</v>
       </c>
     </row>
     <row r="60">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>12371.85544424627</v>
+        <v>9033.859368194988</v>
       </c>
     </row>
     <row r="63">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>32694.62485737791</v>
+        <v>18581.44436977592</v>
       </c>
     </row>
     <row r="66">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8173.656214344477</v>
+        <v>4645.36109244398</v>
       </c>
     </row>
     <row r="68">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>42359.82355503937</v>
+        <v>62318.01724627735</v>
       </c>
     </row>
     <row r="69">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>13230.40252110525</v>
+        <v>14580.75215080433</v>
       </c>
     </row>
     <row r="72">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>31799.86289356963</v>
+        <v>18282.33616228171</v>
       </c>
     </row>
     <row r="75">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>27102.1846897443</v>
+        <v>30674.14675526862</v>
       </c>
     </row>
     <row r="78">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>13596.81570478361</v>
+        <v>7995.451929150265</v>
       </c>
     </row>
     <row r="81">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>17825.58539787152</v>
+        <v>14973.54995390686</v>
       </c>
     </row>
     <row r="84">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4456.39634946788</v>
+        <v>3743.387488476714</v>
       </c>
     </row>
     <row r="86">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>46521.83037408151</v>
+        <v>48268.14024216216</v>
       </c>
     </row>
     <row r="87">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>8899.960541795645</v>
+        <v>10424.63282759292</v>
       </c>
     </row>
     <row r="90">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>31345.33756667055</v>
+        <v>31673.94616488201</v>
       </c>
     </row>
     <row r="93">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>11938.81257539428</v>
+        <v>27147.83862250821</v>
       </c>
     </row>
     <row r="96">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>16141.58126893326</v>
+        <v>19120.85441610223</v>
       </c>
     </row>
     <row r="99">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>11577.80969152855</v>
+        <v>18516.88780787351</v>
       </c>
     </row>
     <row r="102">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2894.452422882137</v>
+        <v>4629.221951968379</v>
       </c>
     </row>
     <row r="104">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>64439.10911114978</v>
+        <v>48166.96773438885</v>
       </c>
     </row>
     <row r="105">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>11173.18427670432</v>
+        <v>17038.93478398161</v>
       </c>
     </row>
     <row r="108">
